--- a/AtchisonRegime/Outputs/USA/USA500_Consumer_Staples/df_regSummary_USA500_Consumer_Staples.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500_Consumer_Staples/df_regSummary_USA500_Consumer_Staples.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>1.255199854093324</v>
+        <v>1.330316098170085</v>
       </c>
       <c r="H2" t="n">
-        <v>3.297952272619971</v>
+        <v>3.325137035561665</v>
       </c>
       <c r="I2" t="n">
         <v>-4.66984504576325</v>
@@ -545,16 +545,16 @@
         <v>9.823783930802669</v>
       </c>
       <c r="K2" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1784807312402021</v>
+        <v>0.1936187364696616</v>
       </c>
       <c r="O2" t="n">
         <v>-0.03344483363254391</v>
@@ -603,7 +603,7 @@
         <v>7.74527627402691</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L3" t="n">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>10.3641980528429</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L4" t="n">
         <v>4</v>
@@ -719,7 +719,7 @@
         <v>9.57292159347422</v>
       </c>
       <c r="K5" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L5" t="n">
         <v>4</v>
